--- a/trading_signals/risk_management/risk_workbook_20260611_031025.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260611_031025.xlsx
@@ -731,7 +731,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-10  ·  Generated 2026-06-11T03:11:29  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-10  ·  Generated 2026-06-24T18:51:00  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1053946.97</v>
+        <v>1054547.31</v>
       </c>
     </row>
     <row r="5">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>19.83</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="11">
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1.12</v>
+        <v>1.111</v>
       </c>
     </row>
     <row r="12">
@@ -822,7 +822,7 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>0.8035</v>
+        <v>0.8018</v>
       </c>
     </row>
     <row r="13">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="14">
@@ -843,7 +843,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>4.03 / 2.02</t>
+          <t>3.94 / 1.97</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>STLD (25.82% NAV)</t>
+          <t>STLD (25.8% NAV)</t>
         </is>
       </c>
     </row>
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>19.83</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="7">
@@ -1276,7 +1276,7 @@
         <v>3397</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>33059296</v>
+        <v>33059301</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>1817</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>18762630</v>
+        <v>18762823</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>0</v>
@@ -1318,7 +1318,7 @@
         <v>1195</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6192562</v>
+        <v>6192571</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -1335,11 +1335,11 @@
           <t>KLAC/REGN</t>
         </is>
       </c>
-      <c r="C11" s="15" t="n">
-        <v>67</v>
+      <c r="C11" s="13" t="n">
+        <v>670</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1063889</v>
+        <v>3046345</v>
       </c>
       <c r="E11" s="17" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
         <v>23</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1102388</v>
+        <v>1102391</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>329</v>
       </c>
       <c r="D13" s="13" t="n">
-        <v>1408638</v>
+        <v>1408637</v>
       </c>
       <c r="E13" s="17" t="n">
         <v>0</v>
@@ -1423,7 +1423,7 @@
         <v>329</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1408638</v>
+        <v>1408637</v>
       </c>
       <c r="E15" s="17" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-40471.56</v>
+        <v>-40494.62</v>
       </c>
       <c r="C4" s="22" t="n">
         <v>-3.84</v>
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-80943.13</v>
+        <v>-80989.23</v>
       </c>
       <c r="C5" s="20" t="n">
         <v>-7.68</v>
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-40471.56</v>
+        <v>-40494.62</v>
       </c>
       <c r="C6" s="22" t="n">
         <v>-3.84</v>
@@ -1629,7 +1629,7 @@
         <v>-43691.92</v>
       </c>
       <c r="C7" s="20" t="n">
-        <v>-4.15</v>
+        <v>-4.14</v>
       </c>
     </row>
   </sheetData>
@@ -1708,7 +1708,7 @@
         </is>
       </c>
       <c r="C4" s="30" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="D4" s="30" t="n">
         <v>3</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="C6" s="30" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="D6" s="30" t="n">
         <v>3</v>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>0.9</v>
+        <v>0.88</v>
       </c>
       <c r="D7" s="32" t="n">
         <v>0.5</v>
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="C8" s="34" t="n">
-        <v>25.82</v>
+        <v>25.8</v>
       </c>
       <c r="D8" s="34" t="n">
         <v>15</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>23.1</v>
+        <v>23.09</v>
       </c>
       <c r="D9" s="32" t="n">
         <v>15</v>
@@ -1864,7 +1864,7 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>15.64</v>
+        <v>15.63</v>
       </c>
       <c r="D10" s="32" t="n">
         <v>15</v>
@@ -2316,10 +2316,10 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>67</v>
+        <v>670</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>2135.64</v>
+        <v>213.56</v>
       </c>
       <c r="G8" s="13" t="n">
         <v>143087.88</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>47</v>
+        <v>470</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>2135.64</v>
+        <v>213.56</v>
       </c>
       <c r="G20" s="13" t="n">
         <v>100375.08</v>
@@ -3571,16 +3571,16 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>15.18</v>
+        <v>15.28</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0.25</v>
+        <v>0.51</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="22" t="n">
-        <v>-14.93</v>
+        <v>-14.77</v>
       </c>
     </row>
     <row r="7">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="B7" s="17" t="n">
-        <v>12.65</v>
+        <v>13.21</v>
       </c>
       <c r="C7" s="17" t="n">
-        <v>19.12</v>
+        <v>23.6</v>
       </c>
       <c r="D7" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>6.47</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="8">
@@ -3609,16 +3609,16 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>25.18</v>
+        <v>25.76</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>25</v>
       </c>
       <c r="E8" s="22" t="n">
-        <v>-21.74</v>
+        <v>-21.86</v>
       </c>
     </row>
     <row r="9">
@@ -3628,16 +3628,16 @@
         </is>
       </c>
       <c r="B9" s="17" t="n">
-        <v>46.99</v>
+        <v>45.75</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>77.19</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>25</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>30.2</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="11">
@@ -3867,30 +3867,30 @@
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>39.13</v>
+        <v>38.94</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>2.6</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>116</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>0.003 (t=0.03)</t>
+          <t>0.003 (t=0.04)</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>-0.074 (t=-0.54)</t>
+          <t>-0.075 (t=-0.55)</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>0.071 (t=0.58)</t>
+          <t>0.073 (t=0.6)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>-0.113 (t=-0.63)</t>
+          <t>-0.11 (t=-0.62)</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -3916,45 +3916,45 @@
         </is>
       </c>
       <c r="B6" s="21" t="n">
-        <v>50.7</v>
+        <v>47.74</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.056</v>
+        <v>0.059</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>116</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>0.034 (t=0.25)</t>
+          <t>0.059 (t=0.41)</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
         <is>
-          <t>-0.088 (t=-0.42)</t>
+          <t>-0.119 (t=-0.54)</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>-0.068 (t=-0.36)</t>
+          <t>-0.059 (t=-0.3)</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>0.221 (t=1.24)</t>
+          <t>0.244 (t=1.32)</t>
         </is>
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>-0.198 (t=-0.71)</t>
+          <t>-0.208 (t=-0.72)</t>
         </is>
       </c>
       <c r="K6" s="17" t="inlineStr">
         <is>
-          <t>-0.136 (t=-1.36)</t>
+          <t>-0.141 (t=-1.36)</t>
         </is>
       </c>
     </row>
@@ -3965,45 +3965,45 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>24.98</v>
+        <v>29.07</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.042</v>
+        <v>0.036</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>116</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>-0.038 (t=-0.26)</t>
+          <t>-0.073 (t=-0.44)</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>-0.042 (t=-0.18)</t>
+          <t>0.001 (t=0.0)</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>0.246 (t=1.2)</t>
+          <t>0.234 (t=1.03)</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>-0.074 (t=-0.39)</t>
+          <t>-0.106 (t=-0.5)</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>0.009 (t=0.03)</t>
+          <t>0.023 (t=0.07)</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
-          <t>-0.072 (t=-0.67)</t>
+          <t>-0.064 (t=-0.53)</t>
         </is>
       </c>
     </row>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>0.145</v>
+        <v>0.178</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>24.903</v>
+        <v>25.364</v>
       </c>
       <c r="D4" s="7" t="n">
         <v>0</v>
@@ -4104,10 +4104,10 @@
         <v>1</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>2.202</v>
+        <v>2.236</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>2.202</v>
+        <v>2.236</v>
       </c>
       <c r="H4" s="7" t="n">
         <v>0</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="B5" s="17" t="n">
-        <v>-0.181</v>
+        <v>-0.413</v>
       </c>
       <c r="C5" s="17" t="n">
-        <v>1.936</v>
+        <v>2.496</v>
       </c>
       <c r="D5" s="17" t="n">
         <v>0</v>
@@ -4132,13 +4132,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="17" t="n">
-        <v>1.537</v>
+        <v>1.6</v>
       </c>
       <c r="G5" s="17" t="n">
-        <v>1.549</v>
+        <v>1.665</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>0.012</v>
+        <v>0.065</v>
       </c>
     </row>
     <row r="6">
@@ -4148,10 +4148,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>1.624</v>
+        <v>1.63</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>31.195</v>
+        <v>29.941</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>0</v>
@@ -4160,10 +4160,10 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4.763</v>
+        <v>4.802</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>4.763</v>
+        <v>4.802</v>
       </c>
       <c r="H6" s="7" t="n">
         <v>0</v>
@@ -4228,28 +4228,28 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.12</v>
+        <v>1.111</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0.8035</v>
+        <v>0.8018</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>9.44</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>76.3</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>4.03</v>
+        <v>3.94</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="J9" s="7" t="n">
         <v>1.409</v>
@@ -4262,13 +4262,13 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>1.368</v>
+        <v>1.164</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.8517</v>
+        <v>0.8111</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>374</v>
+        <v>523</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>9.19</v>
@@ -4277,16 +4277,16 @@
         <v>9.57</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>76.3</v>
+        <v>77</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>6.7</v>
+        <v>5.29</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>3.35</v>
+        <v>2.64</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0.602</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="11">
@@ -4296,13 +4296,13 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>0.761</v>
+        <v>0.829</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>0.7276</v>
+        <v>0.7456</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1108</v>
+        <v>931</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>15.56</v>
@@ -4311,16 +4311,16 @@
         <v>18.48</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>80.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>2.378</v>
+        <v>2.33</v>
       </c>
     </row>
   </sheetData>
@@ -4395,16 +4395,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>87201.33</v>
+        <v>87801.67</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>136276.6</v>
+        <v>136845.07</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>448631.66</v>
+        <v>447777.75</v>
       </c>
     </row>
     <row r="6">
@@ -4452,16 +4452,16 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1583159.53</v>
+        <v>1583759.87</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>1546011.13</v>
+        <v>1546579.6</v>
       </c>
       <c r="D8" s="13" t="n">
         <v>3024360.71</v>
       </c>
       <c r="E8" s="13" t="n">
-        <v>1322016.61</v>
+        <v>1321162.7</v>
       </c>
     </row>
     <row r="9">
@@ -4496,7 +4496,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>937172.17</v>
+        <v>935905.24</v>
       </c>
       <c r="E10" s="15" t="n">
         <v>0</v>
@@ -4515,7 +4515,7 @@
         <v>490890.21</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>1917069.59</v>
+        <v>1915802.66</v>
       </c>
       <c r="E11" s="4" t="n">
         <v>307093.82</v>
@@ -4528,16 +4528,16 @@
         </is>
       </c>
       <c r="B12" s="13" t="n">
-        <v>1053946.97</v>
+        <v>1054547.31</v>
       </c>
       <c r="C12" s="13" t="n">
-        <v>1055120.92</v>
+        <v>1055689.39</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>1107291.12</v>
+        <v>1108558.05</v>
       </c>
       <c r="E12" s="13" t="n">
-        <v>1014922.79</v>
+        <v>1014068.88</v>
       </c>
     </row>
     <row r="13">
@@ -4550,13 +4550,13 @@
         <v>1.409</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>1.327</v>
+        <v>1.326</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2.714</v>
+        <v>2.711</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>0.854</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="14">
@@ -4572,10 +4572,10 @@
         <v>0.396</v>
       </c>
       <c r="D14" s="17" t="n">
-        <v>0.944</v>
+        <v>0.9429999999999999</v>
       </c>
       <c r="E14" s="17" t="n">
-        <v>0.249</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="15">
@@ -4604,16 +4604,16 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>756872.1800000001</v>
+        <v>757472.52</v>
       </c>
       <c r="C16" s="13" t="n">
-        <v>775137.5699999999</v>
+        <v>775706.04</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>506338.57</v>
+        <v>507605.5</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>841474.1800000001</v>
+        <v>840620.27</v>
       </c>
     </row>
     <row r="17">
@@ -4682,7 +4682,7 @@
         <v>909026.52</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>1107291.12</v>
+        <v>1108558.05</v>
       </c>
       <c r="E21" s="4" t="n">
         <v>560149.25</v>
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="13" t="n">
-        <v>917574.22</v>
+        <v>916307.29</v>
       </c>
       <c r="E24" s="15" t="n">
         <v>0</v>
@@ -4758,7 +4758,7 @@
         <v>909026.52</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1107291.12</v>
+        <v>1108558.05</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>560149.25</v>
@@ -4885,16 +4885,16 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>87201.33</v>
+        <v>87801.67</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>136276.6</v>
+        <v>136845.07</v>
       </c>
       <c r="D32" s="15" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="13" t="n">
-        <v>448631.66</v>
+        <v>447777.75</v>
       </c>
     </row>
     <row r="33">
@@ -4904,16 +4904,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>1053946.97</v>
+        <v>1054547.31</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1055120.92</v>
+        <v>1055689.39</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>1107291.12</v>
+        <v>1108558.05</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1014922.79</v>
+        <v>1014068.88</v>
       </c>
     </row>
     <row r="34">
@@ -4976,16 +4976,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>399901.95</v>
+        <v>390679.98</v>
       </c>
       <c r="C39" s="4" t="n">
-        <v>478183.8</v>
+        <v>468937.27</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>488889.66</v>
+        <v>479480.23</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>419168.29</v>
+        <v>409659.12</v>
       </c>
     </row>
     <row r="40">
@@ -5033,16 +5033,16 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>749633.4300000001</v>
+        <v>740411.46</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>673620.47</v>
+        <v>664373.9399999999</v>
       </c>
       <c r="D42" s="13" t="n">
-        <v>671119.97</v>
+        <v>661710.54</v>
       </c>
       <c r="E42" s="13" t="n">
-        <v>781222.91</v>
+        <v>771713.74</v>
       </c>
     </row>
     <row r="43">
@@ -5109,16 +5109,16 @@
         </is>
       </c>
       <c r="B46" s="13" t="n">
-        <v>574836.45</v>
+        <v>565614.48</v>
       </c>
       <c r="C46" s="13" t="n">
-        <v>576366.95</v>
+        <v>567120.42</v>
       </c>
       <c r="D46" s="13" t="n">
-        <v>586521.63</v>
+        <v>577112.2</v>
       </c>
       <c r="E46" s="13" t="n">
-        <v>592738.11</v>
+        <v>583228.9399999999</v>
       </c>
     </row>
     <row r="47">
@@ -5128,16 +5128,16 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.602</v>
+        <v>0.612</v>
       </c>
       <c r="C47" s="7" t="n">
-        <v>0.336</v>
+        <v>0.341</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>0.308</v>
+        <v>0.313</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>0.604</v>
+        <v>0.614</v>
       </c>
     </row>
     <row r="48">
@@ -5153,7 +5153,7 @@
         <v>-0.002</v>
       </c>
       <c r="D48" s="17" t="n">
-        <v>0.019</v>
+        <v>0.02</v>
       </c>
       <c r="E48" s="17" t="n">
         <v>-0.032</v>
@@ -5185,16 +5185,16 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>505589.34</v>
+        <v>496367.37</v>
       </c>
       <c r="C50" s="13" t="n">
-        <v>537668.63</v>
+        <v>528422.1</v>
       </c>
       <c r="D50" s="13" t="n">
-        <v>550413.96</v>
+        <v>541004.53</v>
       </c>
       <c r="E50" s="13" t="n">
-        <v>521081.13</v>
+        <v>511571.96</v>
       </c>
     </row>
     <row r="51">
@@ -5213,7 +5213,7 @@
         <v>-0</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -5466,16 +5466,16 @@
         </is>
       </c>
       <c r="B66" s="13" t="n">
-        <v>399901.95</v>
+        <v>390679.98</v>
       </c>
       <c r="C66" s="13" t="n">
-        <v>478183.8</v>
+        <v>468937.27</v>
       </c>
       <c r="D66" s="13" t="n">
-        <v>488889.66</v>
+        <v>479480.23</v>
       </c>
       <c r="E66" s="13" t="n">
-        <v>419168.29</v>
+        <v>409659.12</v>
       </c>
     </row>
     <row r="67">
@@ -5485,16 +5485,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
-        <v>574836.45</v>
+        <v>565614.48</v>
       </c>
       <c r="C67" s="4" t="n">
-        <v>576366.95</v>
+        <v>567120.42</v>
       </c>
       <c r="D67" s="4" t="n">
-        <v>586521.63</v>
+        <v>577112.2</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>592738.11</v>
+        <v>583228.9399999999</v>
       </c>
     </row>
     <row r="68">
@@ -5566,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="4" t="n">
-        <v>29463.37</v>
+        <v>38118.63</v>
       </c>
     </row>
     <row r="74">
@@ -5623,7 +5623,7 @@
         <v>2842130.4</v>
       </c>
       <c r="E76" s="13" t="n">
-        <v>540793.7</v>
+        <v>549448.96</v>
       </c>
     </row>
     <row r="77">
@@ -5652,13 +5652,13 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>312700.62</v>
+        <v>302878.31</v>
       </c>
       <c r="C78" s="13" t="n">
-        <v>341907.2</v>
+        <v>332092.2</v>
       </c>
       <c r="D78" s="13" t="n">
-        <v>1426061.84</v>
+        <v>1415385.47</v>
       </c>
       <c r="E78" s="15" t="n">
         <v>0</v>
@@ -5671,13 +5671,13 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
-        <v>667116.2</v>
+        <v>657293.89</v>
       </c>
       <c r="C79" s="4" t="n">
-        <v>735543.89</v>
+        <v>725728.89</v>
       </c>
       <c r="D79" s="4" t="n">
-        <v>2321360.92</v>
+        <v>2310684.55</v>
       </c>
       <c r="E79" s="4" t="n">
         <v>118609.02</v>
@@ -5690,16 +5690,16 @@
         </is>
       </c>
       <c r="B80" s="13" t="n">
-        <v>479110.52</v>
+        <v>488932.83</v>
       </c>
       <c r="C80" s="13" t="n">
-        <v>478753.97</v>
+        <v>488568.97</v>
       </c>
       <c r="D80" s="13" t="n">
-        <v>520769.48</v>
+        <v>531445.85</v>
       </c>
       <c r="E80" s="13" t="n">
-        <v>422184.68</v>
+        <v>430839.94</v>
       </c>
     </row>
     <row r="81">
@@ -5709,16 +5709,16 @@
         </is>
       </c>
       <c r="B81" s="7" t="n">
-        <v>2.378</v>
+        <v>2.33</v>
       </c>
       <c r="C81" s="7" t="n">
-        <v>2.52</v>
+        <v>2.469</v>
       </c>
       <c r="D81" s="7" t="n">
-        <v>5.423</v>
+        <v>5.314</v>
       </c>
       <c r="E81" s="7" t="n">
-        <v>1.206</v>
+        <v>1.181</v>
       </c>
     </row>
     <row r="82">
@@ -5728,16 +5728,16 @@
         </is>
       </c>
       <c r="B82" s="17" t="n">
-        <v>0.898</v>
+        <v>0.88</v>
       </c>
       <c r="C82" s="17" t="n">
-        <v>0.876</v>
+        <v>0.858</v>
       </c>
       <c r="D82" s="17" t="n">
-        <v>1.985</v>
+        <v>1.945</v>
       </c>
       <c r="E82" s="17" t="n">
-        <v>0.644</v>
+        <v>0.631</v>
       </c>
     </row>
     <row r="83">
@@ -5766,16 +5766,16 @@
         </is>
       </c>
       <c r="B84" s="13" t="n">
-        <v>251282.84</v>
+        <v>261105.15</v>
       </c>
       <c r="C84" s="13" t="n">
-        <v>237468.94</v>
+        <v>247283.94</v>
       </c>
       <c r="D84" s="18" t="n">
-        <v>-44075.4</v>
+        <v>-33399.03</v>
       </c>
       <c r="E84" s="13" t="n">
-        <v>320393.05</v>
+        <v>329048.31</v>
       </c>
     </row>
     <row r="85">
@@ -5785,13 +5785,13 @@
         </is>
       </c>
       <c r="B85" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C85" s="7" t="n">
         <v>0</v>
       </c>
       <c r="D85" s="7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E85" s="7" t="n">
         <v>-0</v>
@@ -5838,13 +5838,13 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
-        <v>479110.52</v>
+        <v>488932.83</v>
       </c>
       <c r="C89" s="4" t="n">
-        <v>478753.97</v>
+        <v>488568.97</v>
       </c>
       <c r="D89" s="4" t="n">
-        <v>520769.48</v>
+        <v>531445.85</v>
       </c>
       <c r="E89" s="4" t="n">
         <v>390349.13</v>
@@ -5895,13 +5895,13 @@
         </is>
       </c>
       <c r="B92" s="13" t="n">
-        <v>305612.31</v>
+        <v>295790</v>
       </c>
       <c r="C92" s="13" t="n">
-        <v>334034.47</v>
+        <v>324219.47</v>
       </c>
       <c r="D92" s="13" t="n">
-        <v>1408155.86</v>
+        <v>1397479.49</v>
       </c>
       <c r="E92" s="15" t="n">
         <v>0</v>
@@ -5914,13 +5914,13 @@
         </is>
       </c>
       <c r="B93" s="4" t="n">
-        <v>479110.52</v>
+        <v>488932.83</v>
       </c>
       <c r="C93" s="4" t="n">
-        <v>478753.97</v>
+        <v>488568.97</v>
       </c>
       <c r="D93" s="4" t="n">
-        <v>520769.48</v>
+        <v>531445.85</v>
       </c>
       <c r="E93" s="4" t="n">
         <v>390349.13</v>
@@ -6056,7 +6056,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="13" t="n">
-        <v>29463.37</v>
+        <v>38118.63</v>
       </c>
     </row>
     <row r="101">
@@ -6066,16 +6066,16 @@
         </is>
       </c>
       <c r="B101" s="4" t="n">
-        <v>479110.52</v>
+        <v>488932.83</v>
       </c>
       <c r="C101" s="4" t="n">
-        <v>478753.97</v>
+        <v>488568.97</v>
       </c>
       <c r="D101" s="4" t="n">
-        <v>520769.48</v>
+        <v>531445.85</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>422184.68</v>
+        <v>430839.94</v>
       </c>
     </row>
     <row r="102">
@@ -6169,16 +6169,16 @@
         </is>
       </c>
       <c r="B5" s="19" t="n">
-        <v>-1173.95</v>
+        <v>-1142.08</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>-53344.15</v>
+        <v>-54010.74</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>39024.18</v>
+        <v>40478.43</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>132448.18</v>
+        <v>133048.52</v>
       </c>
     </row>
     <row r="6">
@@ -6251,16 +6251,16 @@
         </is>
       </c>
       <c r="B11" s="19" t="n">
-        <v>-1530.5</v>
+        <v>-1505.94</v>
       </c>
       <c r="C11" s="19" t="n">
-        <v>-11685.18</v>
+        <v>-11497.72</v>
       </c>
       <c r="D11" s="19" t="n">
-        <v>-17901.66</v>
+        <v>-17614.46</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>65504.51</v>
+        <v>56282.54</v>
       </c>
     </row>
     <row r="12">
@@ -6333,16 +6333,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>356.55</v>
+        <v>363.86</v>
       </c>
       <c r="C17" s="19" t="n">
-        <v>-41658.96</v>
+        <v>-42513.02</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>56925.84</v>
+        <v>58092.89</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>66943.67</v>
+        <v>76765.98</v>
       </c>
     </row>
     <row r="18">
@@ -6352,16 +6352,16 @@
         </is>
       </c>
       <c r="B18" s="15" t="n">
-        <v>42.84</v>
+        <v>41.49</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>214.18</v>
+        <v>207.45</v>
       </c>
       <c r="D18" s="13" t="n">
-        <v>899.55</v>
+        <v>871.29</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>6511.03</v>
+        <v>6306.51</v>
       </c>
     </row>
     <row r="19">
@@ -6453,13 +6453,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1055120.92</v>
+        <v>1055689.39</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1107291.12</v>
+        <v>1108558.05</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1014922.79</v>
+        <v>1014068.88</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>921498.79</v>
@@ -6472,16 +6472,16 @@
         </is>
       </c>
       <c r="B6" s="18" t="n">
-        <v>-1173.95</v>
+        <v>-1142.08</v>
       </c>
       <c r="C6" s="18" t="n">
-        <v>-53344.15</v>
+        <v>-54010.74</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>39024.18</v>
+        <v>40478.43</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>132448.18</v>
+        <v>133048.52</v>
       </c>
     </row>
     <row r="7">
@@ -6529,16 +6529,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>1053946.97</v>
+        <v>1054547.31</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1053946.97</v>
+        <v>1054547.31</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1053946.97</v>
+        <v>1054547.31</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>1053946.97</v>
+        <v>1054547.31</v>
       </c>
     </row>
     <row r="10">
@@ -6551,13 +6551,13 @@
         <v>-0.11</v>
       </c>
       <c r="C10" s="20" t="n">
-        <v>-4.82</v>
+        <v>-4.87</v>
       </c>
       <c r="D10" s="21" t="n">
-        <v>3.85</v>
+        <v>3.99</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>14.37</v>
+        <v>14.44</v>
       </c>
     </row>
     <row r="11">
@@ -6570,13 +6570,13 @@
         <v>-0.11</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>-9.25</v>
+        <v>-9.41</v>
       </c>
       <c r="D11" s="22" t="n">
-        <v>-9.25</v>
+        <v>-9.41</v>
       </c>
       <c r="E11" s="22" t="n">
-        <v>-9.44</v>
+        <v>-9.470000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>576366.95</v>
+        <v>567120.42</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>586521.63</v>
+        <v>577112.2</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>592738.11</v>
+        <v>583228.9399999999</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>509331.94</v>
@@ -6639,16 +6639,16 @@
         </is>
       </c>
       <c r="B16" s="18" t="n">
-        <v>-1530.5</v>
+        <v>-1505.94</v>
       </c>
       <c r="C16" s="18" t="n">
-        <v>-11685.18</v>
+        <v>-11497.72</v>
       </c>
       <c r="D16" s="18" t="n">
-        <v>-17901.66</v>
+        <v>-17614.46</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>65504.51</v>
+        <v>56282.54</v>
       </c>
     </row>
     <row r="17">
@@ -6696,16 +6696,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>574836.45</v>
+        <v>565614.48</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>574836.45</v>
+        <v>565614.48</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>574836.45</v>
+        <v>565614.48</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>574836.45</v>
+        <v>565614.48</v>
       </c>
     </row>
     <row r="20">
@@ -6724,7 +6724,7 @@
         <v>-3.02</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>12.86</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="21">
@@ -6787,13 +6787,13 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>478753.97</v>
+        <v>488568.97</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>520769.48</v>
+        <v>531445.85</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>422184.68</v>
+        <v>430839.94</v>
       </c>
       <c r="E25" s="4" t="n">
         <v>412166.85</v>
@@ -6806,16 +6806,16 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>356.55</v>
+        <v>363.86</v>
       </c>
       <c r="C26" s="18" t="n">
-        <v>-41658.96</v>
+        <v>-42513.02</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>56925.84</v>
+        <v>58092.89</v>
       </c>
       <c r="E26" s="13" t="n">
-        <v>66943.67</v>
+        <v>76765.98</v>
       </c>
     </row>
     <row r="27">
@@ -6863,16 +6863,16 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>479110.52</v>
+        <v>488932.83</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>479110.52</v>
+        <v>488932.83</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>479110.52</v>
+        <v>488932.83</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>479110.52</v>
+        <v>488932.83</v>
       </c>
     </row>
     <row r="30">
@@ -6891,7 +6891,7 @@
         <v>13.48</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>16.24</v>
+        <v>18.62</v>
       </c>
     </row>
     <row r="31">
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-53344.15</v>
+        <v>-54010.74</v>
       </c>
     </row>
     <row r="5">
@@ -6980,7 +6980,7 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-937172.17</v>
+        <v>-935905.24</v>
       </c>
     </row>
     <row r="7">
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>-372497.23</v>
+        <v>-371896.89</v>
       </c>
     </row>
     <row r="8">
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>87201.33</v>
+        <v>87801.67</v>
       </c>
     </row>
     <row r="11">
@@ -7987,7 +7987,7 @@
         </is>
       </c>
       <c r="B96" s="4" t="n">
-        <v>1011349.68</v>
+        <v>1011202.12</v>
       </c>
     </row>
     <row r="97">
@@ -7997,7 +7997,7 @@
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>1025813.49</v>
+        <v>1025356.19</v>
       </c>
     </row>
     <row r="98">
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="B98" s="4" t="n">
-        <v>1027227.69</v>
+        <v>1026905.51</v>
       </c>
     </row>
     <row r="99">
@@ -8017,7 +8017,7 @@
         </is>
       </c>
       <c r="B99" s="13" t="n">
-        <v>1015143.29</v>
+        <v>1015273.3</v>
       </c>
     </row>
     <row r="100">
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>1002820.85</v>
+        <v>1003025.8</v>
       </c>
     </row>
     <row r="101">
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="B101" s="13" t="n">
-        <v>1012828.92</v>
+        <v>1013098.34</v>
       </c>
     </row>
     <row r="102">
@@ -8047,7 +8047,7 @@
         </is>
       </c>
       <c r="B102" s="4" t="n">
-        <v>1026264.29</v>
+        <v>1026718.34</v>
       </c>
     </row>
     <row r="103">
@@ -8057,7 +8057,7 @@
         </is>
       </c>
       <c r="B103" s="13" t="n">
-        <v>1052540.23</v>
+        <v>1053504.94</v>
       </c>
     </row>
     <row r="104">
@@ -8067,7 +8067,7 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
-        <v>1049865</v>
+        <v>1050844.96</v>
       </c>
     </row>
     <row r="105">
@@ -8077,7 +8077,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>1048836.37</v>
+        <v>1049581.91</v>
       </c>
     </row>
     <row r="106">
@@ -8087,7 +8087,7 @@
         </is>
       </c>
       <c r="B106" s="4" t="n">
-        <v>1048612.65</v>
+        <v>1049200.21</v>
       </c>
     </row>
     <row r="107">
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="B107" s="13" t="n">
-        <v>1042552.87</v>
+        <v>1042965.78</v>
       </c>
     </row>
     <row r="108">
@@ -8107,7 +8107,7 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
-        <v>1048297.88</v>
+        <v>1048734.43</v>
       </c>
     </row>
     <row r="109">
@@ -8117,7 +8117,7 @@
         </is>
       </c>
       <c r="B109" s="13" t="n">
-        <v>1042380.57</v>
+        <v>1042822.5</v>
       </c>
     </row>
     <row r="110">
@@ -8127,7 +8127,7 @@
         </is>
       </c>
       <c r="B110" s="4" t="n">
-        <v>1043779.26</v>
+        <v>1044292.9</v>
       </c>
     </row>
     <row r="111">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="B111" s="13" t="n">
-        <v>1069916.63</v>
+        <v>1070408.83</v>
       </c>
     </row>
     <row r="112">
@@ -8147,7 +8147,7 @@
         </is>
       </c>
       <c r="B112" s="4" t="n">
-        <v>1061158.19</v>
+        <v>1061559.43</v>
       </c>
     </row>
     <row r="113">
@@ -8157,7 +8157,7 @@
         </is>
       </c>
       <c r="B113" s="13" t="n">
-        <v>1074798.87</v>
+        <v>1074879.59</v>
       </c>
     </row>
     <row r="114">
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="B114" s="4" t="n">
-        <v>1080584.35</v>
+        <v>1080503.54</v>
       </c>
     </row>
     <row r="115">
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="B115" s="13" t="n">
-        <v>1087163</v>
+        <v>1086894.67</v>
       </c>
     </row>
     <row r="116">
@@ -8187,7 +8187,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1071651.92</v>
+        <v>1071796.37</v>
       </c>
     </row>
     <row r="117">
@@ -8197,7 +8197,7 @@
         </is>
       </c>
       <c r="B117" s="13" t="n">
-        <v>1065553.29</v>
+        <v>1065522.69</v>
       </c>
     </row>
     <row r="118">
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
-        <v>1080839.51</v>
+        <v>1080563.67</v>
       </c>
     </row>
     <row r="119">
@@ -8217,7 +8217,7 @@
         </is>
       </c>
       <c r="B119" s="13" t="n">
-        <v>1076001.78</v>
+        <v>1075540.76</v>
       </c>
     </row>
     <row r="120">
@@ -8227,7 +8227,7 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
-        <v>1071505.4</v>
+        <v>1070952.2</v>
       </c>
     </row>
     <row r="121">
@@ -8237,7 +8237,7 @@
         </is>
       </c>
       <c r="B121" s="13" t="n">
-        <v>1074307.9</v>
+        <v>1073612.17</v>
       </c>
     </row>
     <row r="122">
@@ -8247,7 +8247,7 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
-        <v>1074845.27</v>
+        <v>1074160.56</v>
       </c>
     </row>
     <row r="123">
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>1085238.37</v>
+        <v>1084460.75</v>
       </c>
     </row>
     <row r="124">
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="B124" s="4" t="n">
-        <v>1086202.03</v>
+        <v>1085444.17</v>
       </c>
     </row>
     <row r="125">
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="B125" s="13" t="n">
-        <v>1093292.29</v>
+        <v>1092531.84</v>
       </c>
     </row>
     <row r="126">
@@ -8287,7 +8287,7 @@
         </is>
       </c>
       <c r="B126" s="4" t="n">
-        <v>1093503.23</v>
+        <v>1092690.79</v>
       </c>
     </row>
     <row r="127">
@@ -8297,7 +8297,7 @@
         </is>
       </c>
       <c r="B127" s="13" t="n">
-        <v>1054764.93</v>
+        <v>1053158.31</v>
       </c>
     </row>
     <row r="128">
@@ -8307,7 +8307,7 @@
         </is>
       </c>
       <c r="B128" s="4" t="n">
-        <v>1051084.85</v>
+        <v>1049512.64</v>
       </c>
     </row>
     <row r="129">
@@ -8317,7 +8317,7 @@
         </is>
       </c>
       <c r="B129" s="13" t="n">
-        <v>1045412.59</v>
+        <v>1043936.06</v>
       </c>
     </row>
     <row r="130">
@@ -8327,7 +8327,7 @@
         </is>
       </c>
       <c r="B130" s="4" t="n">
-        <v>1033859.55</v>
+        <v>1032472.74</v>
       </c>
     </row>
     <row r="131">
@@ -8337,7 +8337,7 @@
         </is>
       </c>
       <c r="B131" s="13" t="n">
-        <v>1040854.38</v>
+        <v>1039556.14</v>
       </c>
     </row>
     <row r="132">
@@ -8347,7 +8347,7 @@
         </is>
       </c>
       <c r="B132" s="4" t="n">
-        <v>1038644.35</v>
+        <v>1037415.03</v>
       </c>
     </row>
     <row r="133">
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="B133" s="13" t="n">
-        <v>1020248.38</v>
+        <v>1019194.66</v>
       </c>
     </row>
     <row r="134">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="B134" s="4" t="n">
-        <v>1014922.79</v>
+        <v>1014068.88</v>
       </c>
     </row>
     <row r="135">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>999863.92</v>
+        <v>999221.6800000001</v>
       </c>
     </row>
     <row r="136">
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="B136" s="4" t="n">
-        <v>1012198.63</v>
+        <v>1011311.18</v>
       </c>
     </row>
     <row r="137">
@@ -8397,7 +8397,7 @@
         </is>
       </c>
       <c r="B137" s="13" t="n">
-        <v>1015396.14</v>
+        <v>1014433.88</v>
       </c>
     </row>
     <row r="138">
@@ -8407,7 +8407,7 @@
         </is>
       </c>
       <c r="B138" s="4" t="n">
-        <v>1012730.63</v>
+        <v>1011774.92</v>
       </c>
     </row>
     <row r="139">
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="B139" s="13" t="n">
-        <v>999176.42</v>
+        <v>998320.26</v>
       </c>
     </row>
     <row r="140">
@@ -8427,7 +8427,7 @@
         </is>
       </c>
       <c r="B140" s="4" t="n">
-        <v>1014831.4</v>
+        <v>1014291.81</v>
       </c>
     </row>
     <row r="141">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="B141" s="13" t="n">
-        <v>1024045.04</v>
+        <v>1023430.49</v>
       </c>
     </row>
     <row r="142">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B142" s="4" t="n">
-        <v>1024091.83</v>
+        <v>1023647.26</v>
       </c>
     </row>
     <row r="143">
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="B143" s="13" t="n">
-        <v>997658.74</v>
+        <v>996791.04</v>
       </c>
     </row>
     <row r="144">
@@ -8467,7 +8467,7 @@
         </is>
       </c>
       <c r="B144" s="4" t="n">
-        <v>1016800.12</v>
+        <v>1016545.25</v>
       </c>
     </row>
     <row r="145">
@@ -8477,7 +8477,7 @@
         </is>
       </c>
       <c r="B145" s="13" t="n">
-        <v>998345.76</v>
+        <v>997800.67</v>
       </c>
     </row>
     <row r="146">
@@ -8487,7 +8487,7 @@
         </is>
       </c>
       <c r="B146" s="4" t="n">
-        <v>992240.33</v>
+        <v>991400.37</v>
       </c>
     </row>
     <row r="147">
@@ -8497,7 +8497,7 @@
         </is>
       </c>
       <c r="B147" s="13" t="n">
-        <v>990259.92</v>
+        <v>989233.28</v>
       </c>
     </row>
     <row r="148">
@@ -8507,7 +8507,7 @@
         </is>
       </c>
       <c r="B148" s="4" t="n">
-        <v>1005628.33</v>
+        <v>1004807.41</v>
       </c>
     </row>
     <row r="149">
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>1098667.75</v>
+        <v>1099781.06</v>
       </c>
     </row>
     <row r="150">
@@ -8527,7 +8527,7 @@
         </is>
       </c>
       <c r="B150" s="4" t="n">
-        <v>1107291.12</v>
+        <v>1108558.05</v>
       </c>
     </row>
     <row r="151">
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="B151" s="13" t="n">
-        <v>1110448.25</v>
+        <v>1111869.67</v>
       </c>
     </row>
     <row r="152">
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="B152" s="4" t="n">
-        <v>1007686.59</v>
+        <v>1007201.77</v>
       </c>
     </row>
     <row r="153">
@@ -8557,7 +8557,7 @@
         </is>
       </c>
       <c r="B153" s="13" t="n">
-        <v>1063120.1</v>
+        <v>1063800.8</v>
       </c>
     </row>
     <row r="154">
@@ -8567,7 +8567,7 @@
         </is>
       </c>
       <c r="B154" s="4" t="n">
-        <v>1055120.92</v>
+        <v>1055689.39</v>
       </c>
     </row>
     <row r="155">
@@ -8577,7 +8577,7 @@
         </is>
       </c>
       <c r="B155" s="13" t="n">
-        <v>1053946.97</v>
+        <v>1054547.31</v>
       </c>
     </row>
   </sheetData>
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1053946.97</v>
+        <v>1054547.31</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>956161.39</v>
@@ -8703,10 +8703,10 @@
         <v>0.405</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>140.93</v>
+        <v>140.85</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>70.47</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K4" s="24" t="n">
         <v>10</v>
@@ -8719,7 +8719,7 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>574836.45</v>
+        <v>565614.48</v>
       </c>
       <c r="C5" s="13" t="n">
         <v>171438.56</v>
@@ -8734,16 +8734,16 @@
         <v>-3358.42</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>0.602</v>
+        <v>0.612</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>-0.006</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>60.23</v>
+        <v>61.21</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>30.12</v>
+        <v>30.61</v>
       </c>
       <c r="K5" s="26" t="n">
         <v>2</v>
@@ -8756,7 +8756,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>479110.52</v>
+        <v>488932.83</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>784722.83</v>
@@ -8771,16 +8771,16 @@
         <v>430307.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2.378</v>
+        <v>2.33</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.898</v>
+        <v>0.88</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>237.76</v>
+        <v>232.98</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>118.88</v>
+        <v>116.49</v>
       </c>
       <c r="K6" s="24" t="n">
         <v>8</v>
@@ -8870,7 +8870,7 @@
         <v>272096.76</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>25.82</v>
+        <v>25.8</v>
       </c>
       <c r="E6" s="23" t="n">
         <v>18.32</v>
@@ -8892,7 +8892,7 @@
         <v>243462.96</v>
       </c>
       <c r="D7" s="21" t="n">
-        <v>23.1</v>
+        <v>23.09</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>16.39</v>
@@ -8914,7 +8914,7 @@
         <v>164822.42</v>
       </c>
       <c r="D8" s="23" t="n">
-        <v>15.64</v>
+        <v>15.63</v>
       </c>
       <c r="E8" s="23" t="n">
         <v>11.1</v>
@@ -9046,7 +9046,7 @@
         <v>53815.65</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>5.11</v>
+        <v>5.1</v>
       </c>
       <c r="E14" s="23" t="n">
         <v>3.62</v>
@@ -9289,7 +9289,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1.321</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="5">
@@ -9299,7 +9299,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>40.83</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="6">

--- a/trading_signals/risk_management/risk_workbook_20260611_031025.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260611_031025.xlsx
@@ -231,7 +231,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -731,7 +731,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-10  ·  Generated 2026-06-24T18:51:00  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-10  ·  Generated 2026-06-25T01:49:33  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1.409</v>
+        <v>1.243</v>
       </c>
     </row>
     <row r="6">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.405</v>
+        <v>0.406</v>
       </c>
     </row>
     <row r="7">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.768</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="8">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>21654.02</v>
+        <v>21466.42</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="10">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>19.82</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="11">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1.409</v>
+        <v>1.243</v>
       </c>
     </row>
     <row r="16">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>29.41</v>
+        <v>33.32</v>
       </c>
     </row>
     <row r="18">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>21654.02</v>
+        <v>21466.42</v>
       </c>
     </row>
     <row r="4">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>30618.39</v>
+        <v>30353.13</v>
       </c>
     </row>
     <row r="5">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>208964.68</v>
+        <v>207154.36</v>
       </c>
     </row>
     <row r="6">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>19.82</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="7">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>12921.92</v>
+        <v>13540.83</v>
       </c>
     </row>
     <row r="8">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>20091.21</v>
+        <v>20936.62</v>
       </c>
     </row>
     <row r="10">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>5283.66</v>
+        <v>5751.57</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>24.4</v>
+        <v>26.79</v>
       </c>
     </row>
     <row r="13">
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>4929.31</v>
+        <v>5031.28</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>22.76</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="14">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>3441.71</v>
+        <v>3513.61</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>15.89</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="15">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>2504.17</v>
+        <v>2357.17</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>11.56</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="16">
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1804.75</v>
+        <v>1748.73</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>8.33</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="17">
@@ -1096,36 +1096,36 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1616.46</v>
+        <v>1692.05</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>7.46</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>BSX/WMB</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>774.73</v>
+        <v>783.95</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>HAS/PFE</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>728.67</v>
+        <v>309.26</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>3.37</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="20">
@@ -1135,23 +1135,10 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>314.67</v>
+        <v>278.81</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>HAS/PFE</t>
-        </is>
-      </c>
-      <c r="B21" s="13" t="n">
-        <v>255.89</v>
-      </c>
-      <c r="C21" s="17" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -1285,19 +1272,19 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>BSX/WMB</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>1817</v>
+        <v>670</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>18762823</v>
+        <v>3046345</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>0</v>
@@ -1306,19 +1293,19 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>BSX/WMB</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1195</v>
+          <t>KLAC/REGN</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>23</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6192571</v>
+        <v>1102391</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -1327,19 +1314,19 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>670</v>
+        <v>329</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>3046345</v>
+        <v>1408637</v>
       </c>
       <c r="E11" s="17" t="n">
         <v>0</v>
@@ -1348,19 +1335,19 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1102391</v>
+        <v>6155217</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -1374,7 +1361,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
@@ -1390,19 +1377,19 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="n">
-        <v>82</v>
+          <t>NUE/MKTX</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>422</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>6155217</v>
+        <v>721296</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1411,19 +1398,19 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>329</v>
+        <v>386</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1408637</v>
+        <v>1103538</v>
       </c>
       <c r="E15" s="17" t="n">
         <v>0</v>
@@ -1432,19 +1419,19 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>422</v>
+        <v>358</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>721296</v>
+        <v>1031090</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1458,11 +1445,11 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>386</v>
+        <v>628</v>
       </c>
       <c r="D17" s="13" t="n">
         <v>1103538</v>
@@ -1474,19 +1461,19 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>358</v>
+        <v>2247</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1031090</v>
+        <v>8680193</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1495,19 +1482,19 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>STLD/FMC</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>628</v>
+        <v>2168</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>1103538</v>
+        <v>8809289</v>
       </c>
       <c r="E19" s="17" t="n">
         <v>0</v>
@@ -1516,19 +1503,19 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2247</v>
+        <v>470</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>8680193</v>
+        <v>3046345</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
@@ -1587,10 +1574,10 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-40494.62</v>
+        <v>-42392.8</v>
       </c>
       <c r="C4" s="22" t="n">
-        <v>-3.84</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="5">
@@ -1600,10 +1587,10 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-80989.23</v>
+        <v>-84785.60000000001</v>
       </c>
       <c r="C5" s="20" t="n">
-        <v>-7.68</v>
+        <v>-8.039999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1613,10 +1600,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-40494.62</v>
+        <v>-42392.8</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>-3.84</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="7">
@@ -1708,7 +1695,7 @@
         </is>
       </c>
       <c r="C4" s="30" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="D4" s="30" t="n">
         <v>3</v>
@@ -1734,7 +1721,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D5" s="30" t="n">
         <v>0.5</v>
@@ -1879,28 +1866,28 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="31" t="inlineStr">
         <is>
           <t>sector_net</t>
         </is>
       </c>
-      <c r="B11" s="30" t="inlineStr">
+      <c r="B11" s="32" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="C11" s="30" t="n">
-        <v>29.41</v>
-      </c>
-      <c r="D11" s="30" t="n">
+      <c r="C11" s="32" t="n">
+        <v>33.32</v>
+      </c>
+      <c r="D11" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="30" t="n">
+      <c r="E11" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="30" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>amber</t>
         </is>
       </c>
     </row>
@@ -1916,7 +1903,7 @@
         </is>
       </c>
       <c r="C12" s="30" t="n">
-        <v>16.32</v>
+        <v>18.49</v>
       </c>
       <c r="D12" s="30" t="n">
         <v>20</v>
@@ -1942,7 +1929,7 @@
         </is>
       </c>
       <c r="C13" s="34" t="n">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="D13" s="34" t="n">
         <v>0.3</v>
@@ -1968,7 +1955,7 @@
         </is>
       </c>
       <c r="C14" s="30" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="D14" s="30" t="n">
         <v>3</v>
@@ -1994,7 +1981,7 @@
         </is>
       </c>
       <c r="C15" s="30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="30" t="n">
         <v>8</v>
@@ -2044,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2209,36 +2196,36 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>MRPT</t>
+          <t>MTFS</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>BSX/WMB</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>-1817</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>48.34</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>-87833.78</v>
+        <v>670</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>213.56</v>
+      </c>
+      <c r="G6" s="13" t="n">
+        <v>143087.88</v>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I6" s="17" t="n">
@@ -2246,43 +2233,43 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>tight_stop</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>MRPT</t>
+          <t>MTFS</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>BSX/WMB</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="E7" s="24" t="n">
-        <v>1195</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>72.26000000000001</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>86350.7</v>
+        <v>-23</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>601.65</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>-13837.95</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
@@ -2290,7 +2277,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>tight_stop</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2289,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -2316,17 +2303,17 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>670</v>
+        <v>329</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>213.56</v>
+        <v>250.49</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>143087.88</v>
+        <v>82411.21000000001</v>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>materials</t>
         </is>
       </c>
       <c r="I8" s="17" t="n">
@@ -2334,7 +2321,7 @@
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>conservative</t>
         </is>
       </c>
     </row>
@@ -2346,12 +2333,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2360,17 +2347,17 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-23</v>
+        <v>-82</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>601.65</v>
+        <v>284.22</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>-13837.95</v>
+        <v>-23306.04</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I9" s="7" t="n">
@@ -2378,7 +2365,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>conservative</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2377,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -2422,7 +2409,7 @@
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t>conservative</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2421,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2448,13 +2435,13 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-82</v>
+        <v>-422</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>284.22</v>
+        <v>116.11</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>-23306.04</v>
+        <v>-48998.42</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -2466,7 +2453,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>conservative</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2478,12 +2465,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -2492,13 +2479,13 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>329</v>
+        <v>386</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>250.49</v>
+        <v>268.34</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>82411.21000000001</v>
+        <v>103579.24</v>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
@@ -2506,11 +2493,11 @@
         </is>
       </c>
       <c r="I12" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>no_reversal_protection</t>
         </is>
       </c>
     </row>
@@ -2522,12 +2509,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2536,25 +2523,25 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-422</v>
+        <v>-358</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>116.11</v>
+        <v>144.82</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>-48998.42</v>
+        <v>-51845.56</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I13" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>no_reversal_protection</t>
         </is>
       </c>
     </row>
@@ -2566,7 +2553,7 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
@@ -2580,13 +2567,13 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>386</v>
+        <v>628</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>268.34</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>103579.24</v>
+        <v>168517.52</v>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
@@ -2598,7 +2585,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>no_reversal_protection</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2610,12 +2597,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2624,17 +2611,17 @@
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-358</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>144.82</v>
+        <v>-6843</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>10.8</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>-51845.56</v>
+        <v>-73904.39999999999</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>food</t>
         </is>
       </c>
       <c r="I15" s="7" t="n">
@@ -2642,7 +2629,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>no_reversal_protection</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2641,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>STLD/FMC</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -2668,25 +2655,25 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>628</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>268.34</v>
+        <v>2247</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>23.95</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>168517.52</v>
+        <v>53815.65</v>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>realestate</t>
         </is>
       </c>
       <c r="I16" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>long_term_kalman</t>
         </is>
       </c>
     </row>
@@ -2698,12 +2685,12 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>STLD/FMC</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>FMC</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2712,13 +2699,13 @@
         </is>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-6843</v>
+        <v>-2168</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10.8</v>
+        <v>19.82</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>-73904.39999999999</v>
+        <v>-42969.76</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -2726,11 +2713,11 @@
         </is>
       </c>
       <c r="I17" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>long_term_kalman</t>
         </is>
       </c>
     </row>
@@ -2742,12 +2729,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -2756,17 +2743,17 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>2247</v>
-      </c>
-      <c r="F18" s="15" t="n">
-        <v>23.95</v>
+        <v>470</v>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>213.56</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>53815.65</v>
+        <v>100375.08</v>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>realestate</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I18" s="17" t="n">
@@ -2774,7 +2761,7 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>long_term_kalman</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2786,12 +2773,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>TRMB</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2800,17 +2787,17 @@
         </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>-2168</v>
+        <v>-972</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>19.82</v>
+        <v>50.6</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>-42969.76</v>
+        <v>-49183.2</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="I19" s="7" t="n">
@@ -2818,7 +2805,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>long_term_kalman</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2830,12 +2817,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
+          <t>UNH/ULTA</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
@@ -2844,17 +2831,17 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>470</v>
+        <v>124</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>213.56</v>
+        <v>407.46</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>100375.08</v>
+        <v>50525.04</v>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I20" s="17" t="n">
@@ -2862,7 +2849,7 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>short_term_beta_neutral</t>
         </is>
       </c>
     </row>
@@ -2874,12 +2861,12 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
+          <t>UNH/ULTA</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -2888,111 +2875,23 @@
         </is>
       </c>
       <c r="E21" s="24" t="n">
-        <v>-972</v>
-      </c>
-      <c r="F21" s="11" t="n">
-        <v>50.6</v>
+        <v>-107</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>470.75</v>
       </c>
       <c r="G21" s="19" t="n">
-        <v>-49183.2</v>
+        <v>-50370.25</v>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>industrial</t>
+          <t>food</t>
         </is>
       </c>
       <c r="I21" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>monthly_aligned_windows</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>MTFS</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>UNH/ULTA</t>
-        </is>
-      </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>UNH</t>
-        </is>
-      </c>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="E22" s="26" t="n">
-        <v>124</v>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>407.46</v>
-      </c>
-      <c r="G22" s="13" t="n">
-        <v>50525.04</v>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>health</t>
-        </is>
-      </c>
-      <c r="I22" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="17" t="inlineStr">
-        <is>
-          <t>short_term_beta_neutral</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>MTFS</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>UNH/ULTA</t>
-        </is>
-      </c>
-      <c r="C23" s="7" t="inlineStr">
-        <is>
-          <t>ULTA</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>short</t>
-        </is>
-      </c>
-      <c r="E23" s="24" t="n">
-        <v>-107</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>470.75</v>
-      </c>
-      <c r="G23" s="19" t="n">
-        <v>-50370.25</v>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>short_term_beta_neutral</t>
         </is>
@@ -3012,7 +2911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3102,31 +3001,31 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>MRPT</t>
+          <t>MTFS</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>BSX/WMB</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>1927.19</v>
+        <v>9083.059999999999</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>174184.48</v>
+        <v>156925.83</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>tight_stop</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
     </row>
@@ -3138,21 +3037,21 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>9083.059999999999</v>
+        <v>4040.63</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>156925.83</v>
+        <v>105717.25</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>conservative</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -3169,21 +3068,21 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>4040.63</v>
+        <v>6039.67</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>105717.25</v>
+        <v>131409.63</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>conservative</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -3200,21 +3099,21 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>6039.67</v>
+          <t>STLD/UHS</t>
+        </is>
+      </c>
+      <c r="C8" s="35" t="n">
+        <v>-8.06</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>131409.63</v>
+        <v>155424.8</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>no_reversal_protection</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
@@ -3231,21 +3130,21 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
-        </is>
-      </c>
-      <c r="C9" s="35" t="n">
-        <v>-8.06</v>
+          <t>STLD/FMC</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>2768.82</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>155424.8</v>
+        <v>242421.92</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>no_reversal_protection</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -3262,21 +3161,21 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>STLD/FMC</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>2768.82</v>
+        <v>2281.05</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>242421.92</v>
+        <v>96785.41</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>long_term_kalman</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -3293,21 +3192,21 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2281.05</v>
+        <v>2108.89</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>96785.41</v>
+        <v>149558.28</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>long_term_kalman</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -3324,55 +3223,24 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="n">
-        <v>2108.89</v>
+          <t>UNH/ULTA</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>78.09</v>
       </c>
       <c r="D12" s="13" t="n">
-        <v>149558.28</v>
+        <v>100895.29</v>
       </c>
       <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="17" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>short_term_beta_neutral</t>
         </is>
       </c>
       <c r="G12" s="17" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>MTFS</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>UNH/ULTA</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="n">
-        <v>78.09</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>100895.29</v>
-      </c>
-      <c r="E13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>short_term_beta_neutral</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3506,7 +3374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3666,7 +3534,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>24.4</v>
+        <v>26.79</v>
       </c>
     </row>
     <row r="14">
@@ -3676,7 +3544,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>22.76</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="15">
@@ -3686,7 +3554,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>15.89</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="16">
@@ -3696,7 +3564,7 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>11.56</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="17">
@@ -3706,7 +3574,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>8.33</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="18">
@@ -3716,27 +3584,27 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>7.46</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>BSX/WMB</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>3.58</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>HAS/PFE</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>3.37</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="21">
@@ -3746,17 +3614,7 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>HAS/PFE</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -4252,7 +4110,7 @@
         <v>1.97</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.409</v>
+        <v>1.243</v>
       </c>
     </row>
     <row r="10">
@@ -4286,7 +4144,7 @@
         <v>2.64</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0.612</v>
+        <v>0.304</v>
       </c>
     </row>
     <row r="11">
@@ -4395,7 +4253,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>87801.67</v>
+        <v>175909.04</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>136845.07</v>
@@ -4414,7 +4272,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>539796.8100000001</v>
+        <v>450206.36</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>500708.01</v>
@@ -4433,7 +4291,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>956161.39</v>
+        <v>869810.6899999999</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>909026.52</v>
@@ -4452,7 +4310,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1583759.87</v>
+        <v>1495926.09</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1546579.6</v>
@@ -4471,7 +4329,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>529212.5600000001</v>
+        <v>441378.78</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>490890.21</v>
@@ -4509,7 +4367,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>529212.5600000001</v>
+        <v>441378.78</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>490890.21</v>
@@ -4547,7 +4405,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1.409</v>
+        <v>1.243</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>1.326</v>
@@ -4566,7 +4424,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>0.405</v>
+        <v>0.406</v>
       </c>
       <c r="C14" s="17" t="n">
         <v>0.396</v>
@@ -4585,7 +4443,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>297074.79</v>
+        <v>262237.89</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>279983.35</v>
@@ -4604,7 +4462,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>757472.52</v>
+        <v>792309.42</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>775706.04</v>
@@ -4676,7 +4534,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>956161.39</v>
+        <v>869810.6899999999</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>909026.52</v>
@@ -4714,7 +4572,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>956161.39</v>
+        <v>869810.6899999999</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>909026.52</v>
@@ -4752,7 +4610,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>956161.39</v>
+        <v>869810.6899999999</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>909026.52</v>
@@ -4771,7 +4629,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>10584.25</v>
+        <v>8827.58</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>9817.799999999999</v>
@@ -4790,7 +4648,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>10584.25</v>
+        <v>8827.58</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>9817.799999999999</v>
@@ -4809,7 +4667,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>529212.5600000001</v>
+        <v>441378.78</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>490890.21</v>
@@ -4828,7 +4686,7 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>529212.5600000001</v>
+        <v>441378.78</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>490890.21</v>
@@ -4866,7 +4724,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>10584.25</v>
+        <v>8827.58</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>9817.799999999999</v>
@@ -4885,7 +4743,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>87801.67</v>
+        <v>175909.04</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>136845.07</v>
@@ -4976,7 +4834,7 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>390679.98</v>
+        <v>478787.36</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>468937.27</v>
@@ -4995,7 +4853,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>178292.92</v>
+        <v>88702.46000000001</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>99198.59</v>
@@ -5014,7 +4872,7 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>171438.56</v>
+        <v>85087.86</v>
       </c>
       <c r="C41" s="4" t="n">
         <v>96238.08</v>
@@ -5033,7 +4891,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>740411.46</v>
+        <v>652577.6800000001</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>664373.9399999999</v>
@@ -5052,7 +4910,7 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>174796.98</v>
+        <v>86963.2</v>
       </c>
       <c r="C43" s="4" t="n">
         <v>97253.52</v>
@@ -5090,7 +4948,7 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>174796.98</v>
+        <v>86963.2</v>
       </c>
       <c r="C45" s="4" t="n">
         <v>97253.52</v>
@@ -5128,7 +4986,7 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.612</v>
+        <v>0.304</v>
       </c>
       <c r="C47" s="7" t="n">
         <v>0.341</v>
@@ -5147,7 +5005,7 @@
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>-0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="C48" s="17" t="n">
         <v>-0.002</v>
@@ -5166,7 +5024,7 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>69247.11</v>
+        <v>34410.21</v>
       </c>
       <c r="C49" s="4" t="n">
         <v>38698.32</v>
@@ -5185,7 +5043,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>496367.37</v>
+        <v>531204.27</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>528422.1</v>
@@ -5257,7 +5115,7 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>171438.56</v>
+        <v>85087.86</v>
       </c>
       <c r="C55" s="4" t="n">
         <v>96238.08</v>
@@ -5295,7 +5153,7 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>171438.56</v>
+        <v>85087.86</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>96238.08</v>
@@ -5333,7 +5191,7 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>171438.56</v>
+        <v>85087.86</v>
       </c>
       <c r="C59" s="4" t="n">
         <v>96238.08</v>
@@ -5352,7 +5210,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>3495.94</v>
+        <v>1739.26</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1945.07</v>
@@ -5371,7 +5229,7 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>3495.94</v>
+        <v>1739.26</v>
       </c>
       <c r="C61" s="4" t="n">
         <v>1945.07</v>
@@ -5390,7 +5248,7 @@
         </is>
       </c>
       <c r="B62" s="13" t="n">
-        <v>174796.98</v>
+        <v>86963.2</v>
       </c>
       <c r="C62" s="13" t="n">
         <v>97253.52</v>
@@ -5409,7 +5267,7 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>174796.98</v>
+        <v>86963.2</v>
       </c>
       <c r="C63" s="4" t="n">
         <v>97253.52</v>
@@ -5447,7 +5305,7 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>3495.94</v>
+        <v>1739.26</v>
       </c>
       <c r="C65" s="4" t="n">
         <v>1945.07</v>
@@ -5466,7 +5324,7 @@
         </is>
       </c>
       <c r="B66" s="13" t="n">
-        <v>390679.98</v>
+        <v>478787.36</v>
       </c>
       <c r="C66" s="13" t="n">
         <v>468937.27</v>
@@ -6207,7 +6065,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>26622.06</v>
+        <v>24694.87</v>
       </c>
     </row>
     <row r="9">
@@ -6288,8 +6146,8 @@
           <t>Current unrealized PnL</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>229.91</v>
+      <c r="B13" s="19" t="n">
+        <v>-1697.28</v>
       </c>
     </row>
     <row r="15">
@@ -6970,7 +6828,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>618019.09</v>
+        <v>616536.01</v>
       </c>
     </row>
     <row r="6">
@@ -6990,7 +6848,7 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>-371896.89</v>
+        <v>-373379.97</v>
       </c>
     </row>
     <row r="8">
@@ -7010,7 +6868,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>87801.67</v>
+        <v>175909.04</v>
       </c>
     </row>
     <row r="11">
@@ -8685,31 +8543,31 @@
         <v>1054547.31</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>956161.39</v>
+        <v>869810.6899999999</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>529212.5600000001</v>
+        <v>441378.78</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1485373.95</v>
+        <v>1311189.47</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>426948.83</v>
+        <v>428431.91</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.409</v>
+        <v>1.243</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.405</v>
+        <v>0.406</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>140.85</v>
+        <v>124.34</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>70.43000000000001</v>
+        <v>62.17</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -8722,31 +8580,31 @@
         <v>565614.48</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>171438.56</v>
+        <v>85087.86</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>174796.98</v>
+        <v>86963.2</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>346235.54</v>
+        <v>172051.06</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>-3358.42</v>
+        <v>-1875.34</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>0.612</v>
+        <v>0.304</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>-0.006</v>
+        <v>-0.003</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>61.21</v>
+        <v>30.42</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>30.61</v>
+        <v>15.21</v>
       </c>
       <c r="K5" s="26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -8800,7 +8658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8821,7 +8679,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>HHI=0.1078  ·  effective N pairs=9.3  ·  max pair=16.32% of gross</t>
+          <t>HHI=0.1207  ·  effective N pairs=8.3  ·  max pair=18.49% of gross</t>
         </is>
       </c>
     </row>
@@ -8873,7 +8731,7 @@
         <v>25.8</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>18.32</v>
+        <v>20.75</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>2</v>
@@ -8895,7 +8753,7 @@
         <v>23.09</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>16.39</v>
+        <v>18.57</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>2</v>
@@ -8917,7 +8775,7 @@
         <v>15.63</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>11.1</v>
+        <v>12.57</v>
       </c>
       <c r="F8" s="24" t="n">
         <v>2</v>
@@ -8926,20 +8784,20 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>BSX</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>87833.78</v>
+        <v>86963.2</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>-87833.78</v>
+        <v>-86963.2</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>8.33</v>
+        <v>8.25</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>5.91</v>
+        <v>6.63</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>1</v>
@@ -8948,20 +8806,20 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>86963.2</v>
-      </c>
-      <c r="C10" s="19" t="n">
-        <v>-86963.2</v>
+        <v>85087.86</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>85087.86</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>8.25</v>
+        <v>8.07</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>5.85</v>
+        <v>6.49</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>1</v>
@@ -8970,20 +8828,20 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>WMB</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>86350.7</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>86350.7</v>
+        <v>73904.39999999999</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>-73904.39999999999</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>8.19</v>
+        <v>7.01</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>5.81</v>
+        <v>5.64</v>
       </c>
       <c r="F11" s="26" t="n">
         <v>1</v>
@@ -8992,20 +8850,20 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>85087.86</v>
+        <v>53815.65</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>85087.86</v>
+        <v>53815.65</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>8.07</v>
+        <v>5.1</v>
       </c>
       <c r="E12" s="23" t="n">
-        <v>5.73</v>
+        <v>4.1</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>1</v>
@@ -9014,20 +8872,20 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>FMC</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>73904.39999999999</v>
+        <v>51845.56</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>-73904.39999999999</v>
+        <v>-51845.56</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>7.01</v>
+        <v>4.92</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>4.98</v>
+        <v>3.95</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>1</v>
@@ -9036,20 +8894,20 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>53815.65</v>
+        <v>50525.04</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>53815.65</v>
+        <v>50525.04</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>5.1</v>
+        <v>4.79</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>1</v>
@@ -9058,20 +8916,20 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>ULTA</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>51845.56</v>
+        <v>50370.25</v>
       </c>
       <c r="C15" s="18" t="n">
-        <v>-51845.56</v>
+        <v>-50370.25</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>4.92</v>
+        <v>4.78</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>3.49</v>
+        <v>3.84</v>
       </c>
       <c r="F15" s="26" t="n">
         <v>1</v>
@@ -9127,121 +8985,102 @@
         <v>436919.18</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>29.41</v>
+        <v>33.32</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>50525.04</v>
+        <v>243462.96</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>240480.49</v>
-      </c>
-      <c r="D21" s="18" t="n">
-        <v>-189955.45</v>
+        <v>72304.46000000001</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>171158.5</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>-12.79</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>health</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>243462.96</v>
+        <v>50525.04</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>72304.46000000001</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>171158.5</v>
+        <v>152646.71</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>-102121.67</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>11.52</v>
+        <v>-7.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>energy</t>
+          <t>food</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>86350.7</v>
-      </c>
-      <c r="C23" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>86350.7</v>
+        <v>85087.86</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>167244.41</v>
+      </c>
+      <c r="D23" s="18" t="n">
+        <v>-82156.55</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>5.81</v>
+        <v>-6.27</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>realestate</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>85087.86</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>167244.41</v>
-      </c>
-      <c r="D24" s="19" t="n">
-        <v>-82156.55</v>
+        <v>53815.65</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>53815.65</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>-5.53</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>realestate</t>
-        </is>
-      </c>
-      <c r="B25" s="13" t="n">
-        <v>53815.65</v>
-      </c>
-      <c r="C25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>53815.65</v>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>49183.2</v>
+      </c>
+      <c r="D25" s="18" t="n">
+        <v>-49183.2</v>
       </c>
       <c r="E25" s="17" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>industrial</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>49183.2</v>
-      </c>
-      <c r="D26" s="19" t="n">
-        <v>-49183.2</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <v>-3.31</v>
+        <v>-3.75</v>
       </c>
     </row>
   </sheetData>
@@ -9258,7 +9097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9279,7 +9118,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.768</v>
+        <v>0.804</v>
       </c>
     </row>
     <row r="4">
@@ -9289,7 +9128,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1.32</v>
+        <v>1.284</v>
       </c>
     </row>
     <row r="5">
@@ -9340,67 +9179,57 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>29.41</v>
+        <v>33.32</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>health</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="n">
-        <v>-12.79</v>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="n">
+        <v>13.05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="n">
-        <v>11.52</v>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="n">
+        <v>-7.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>energy</t>
-        </is>
-      </c>
-      <c r="B13" s="21" t="n">
-        <v>5.81</v>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n">
+        <v>-6.27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="n">
-        <v>-5.53</v>
+          <t>realestate</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>realestate</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="n">
-        <v>3.62</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="B16" s="22" t="n">
-        <v>-3.31</v>
+      <c r="B15" s="20" t="n">
+        <v>-3.75</v>
       </c>
     </row>
   </sheetData>

--- a/trading_signals/risk_management/risk_workbook_20260611_031025.xlsx
+++ b/trading_signals/risk_management/risk_workbook_20260611_031025.xlsx
@@ -231,7 +231,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -731,7 +731,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Signal date 2026-06-10  ·  Generated 2026-06-25T01:49:33  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
+          <t>Signal date 2026-06-10  ·  Generated 2026-06-25T02:04:51  ·  Scope: MRPT+MTFS pairs book (model-based, broker-reconciled)</t>
         </is>
       </c>
     </row>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1.243</v>
+        <v>1.409</v>
       </c>
     </row>
     <row r="6">
@@ -762,7 +762,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>0.406</v>
+        <v>0.405</v>
       </c>
     </row>
     <row r="7">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>0.804</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="8">
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>21466.42</v>
+        <v>21654.02</v>
       </c>
     </row>
     <row r="9">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="10">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="B10" s="5" t="n">
-        <v>19.64</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="11">
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="B15" s="5" t="n">
-        <v>1.243</v>
+        <v>1.409</v>
       </c>
     </row>
     <row r="16">
@@ -876,7 +876,7 @@
         </is>
       </c>
       <c r="B17" s="5" t="n">
-        <v>33.32</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="18">
@@ -886,7 +886,7 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -925,7 +925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>21466.42</v>
+        <v>21654.02</v>
       </c>
     </row>
     <row r="4">
@@ -957,7 +957,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>30353.13</v>
+        <v>30618.39</v>
       </c>
     </row>
     <row r="5">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>207154.36</v>
+        <v>208964.68</v>
       </c>
     </row>
     <row r="6">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>19.64</v>
+        <v>19.82</v>
       </c>
     </row>
     <row r="7">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>13540.83</v>
+        <v>12921.92</v>
       </c>
     </row>
     <row r="8">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>20936.62</v>
+        <v>20091.21</v>
       </c>
     </row>
     <row r="10">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>5751.57</v>
+        <v>5283.66</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>26.79</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="13">
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>5031.28</v>
+        <v>4929.31</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>23.44</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="14">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>3513.61</v>
+        <v>3441.71</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>16.37</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="15">
@@ -1070,10 +1070,10 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>2357.17</v>
+        <v>2504.17</v>
       </c>
       <c r="C15" s="17" t="n">
-        <v>10.98</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="16">
@@ -1083,10 +1083,10 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1748.73</v>
+        <v>1804.75</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>8.15</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="17">
@@ -1096,36 +1096,36 @@
         </is>
       </c>
       <c r="B17" s="13" t="n">
-        <v>1692.05</v>
+        <v>1616.46</v>
       </c>
       <c r="C17" s="17" t="n">
-        <v>7.88</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>BSX/WMB</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>783.95</v>
+        <v>774.73</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>HAS/PFE</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>309.26</v>
+        <v>728.67</v>
       </c>
       <c r="C19" s="17" t="n">
-        <v>1.44</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="20">
@@ -1135,10 +1135,23 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>278.81</v>
+        <v>314.67</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>HAS/PFE</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>255.89</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>
@@ -1272,19 +1285,19 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>BSX/WMB</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>670</v>
+        <v>1817</v>
       </c>
       <c r="D9" s="13" t="n">
-        <v>3046345</v>
+        <v>18762823</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>0</v>
@@ -1293,19 +1306,19 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>23</v>
+          <t>BSX/WMB</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1195</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1102391</v>
+        <v>6192571</v>
       </c>
       <c r="E10" s="7" t="n">
         <v>0</v>
@@ -1314,19 +1327,19 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B11" s="17" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>329</v>
+        <v>670</v>
       </c>
       <c r="D11" s="13" t="n">
-        <v>1408637</v>
+        <v>3046345</v>
       </c>
       <c r="E11" s="17" t="n">
         <v>0</v>
@@ -1335,19 +1348,19 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C12" s="11" t="n">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6155217</v>
+        <v>1102391</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>0</v>
@@ -1361,7 +1374,7 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
@@ -1377,19 +1390,19 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>422</v>
+          <t>NUE/INTU</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>82</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>721296</v>
+        <v>6155217</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>0</v>
@@ -1398,19 +1411,19 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>386</v>
+        <v>329</v>
       </c>
       <c r="D15" s="13" t="n">
-        <v>1103538</v>
+        <v>1408637</v>
       </c>
       <c r="E15" s="17" t="n">
         <v>0</v>
@@ -1419,19 +1432,19 @@
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>358</v>
+        <v>422</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1031090</v>
+        <v>721296</v>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
@@ -1445,11 +1458,11 @@
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>STLD/FMC</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>628</v>
+        <v>386</v>
       </c>
       <c r="D17" s="13" t="n">
         <v>1103538</v>
@@ -1461,19 +1474,19 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2247</v>
+        <v>358</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>8680193</v>
+        <v>1031090</v>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
@@ -1482,19 +1495,19 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>2168</v>
+        <v>628</v>
       </c>
       <c r="D19" s="13" t="n">
-        <v>8809289</v>
+        <v>1103538</v>
       </c>
       <c r="E19" s="17" t="n">
         <v>0</v>
@@ -1503,19 +1516,19 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>470</v>
+        <v>2247</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>3046345</v>
+        <v>8680193</v>
       </c>
       <c r="E20" s="7" t="n">
         <v>0</v>
@@ -1574,10 +1587,10 @@
         </is>
       </c>
       <c r="B4" s="19" t="n">
-        <v>-42392.8</v>
+        <v>-40494.62</v>
       </c>
       <c r="C4" s="22" t="n">
-        <v>-4.02</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="5">
@@ -1587,10 +1600,10 @@
         </is>
       </c>
       <c r="B5" s="18" t="n">
-        <v>-84785.60000000001</v>
+        <v>-80989.23</v>
       </c>
       <c r="C5" s="20" t="n">
-        <v>-8.039999999999999</v>
+        <v>-7.68</v>
       </c>
     </row>
     <row r="6">
@@ -1600,10 +1613,10 @@
         </is>
       </c>
       <c r="B6" s="19" t="n">
-        <v>-42392.8</v>
+        <v>-40494.62</v>
       </c>
       <c r="C6" s="22" t="n">
-        <v>-4.02</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="7">
@@ -1695,7 +1708,7 @@
         </is>
       </c>
       <c r="C4" s="30" t="n">
-        <v>0.3</v>
+        <v>0.61</v>
       </c>
       <c r="D4" s="30" t="n">
         <v>3</v>
@@ -1721,7 +1734,7 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="D5" s="30" t="n">
         <v>0.5</v>
@@ -1866,28 +1879,28 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>sector_net</t>
         </is>
       </c>
-      <c r="B11" s="32" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>materials</t>
         </is>
       </c>
-      <c r="C11" s="32" t="n">
-        <v>33.32</v>
-      </c>
-      <c r="D11" s="32" t="n">
+      <c r="C11" s="30" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="D11" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="32" t="n">
+      <c r="E11" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="F11" s="32" t="inlineStr">
-        <is>
-          <t>amber</t>
+      <c r="F11" s="30" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
     </row>
@@ -1903,7 +1916,7 @@
         </is>
       </c>
       <c r="C12" s="30" t="n">
-        <v>18.49</v>
+        <v>16.32</v>
       </c>
       <c r="D12" s="30" t="n">
         <v>20</v>
@@ -1929,7 +1942,7 @@
         </is>
       </c>
       <c r="C13" s="34" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="D13" s="34" t="n">
         <v>0.3</v>
@@ -1955,7 +1968,7 @@
         </is>
       </c>
       <c r="C14" s="30" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="D14" s="30" t="n">
         <v>3</v>
@@ -1981,7 +1994,7 @@
         </is>
       </c>
       <c r="C15" s="30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="30" t="n">
         <v>8</v>
@@ -2031,7 +2044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2196,36 +2209,36 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>MTFS</t>
+          <t>MRPT</t>
         </is>
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>BSX/WMB</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>670</v>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>213.56</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <v>143087.88</v>
+        <v>-1817</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>-87833.78</v>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I6" s="17" t="n">
@@ -2233,43 +2246,43 @@
       </c>
       <c r="J6" s="17" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>tight_stop</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>MTFS</t>
+          <t>MRPT</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>BSX/WMB</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>REGN</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="E7" s="24" t="n">
-        <v>-23</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>601.65</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>-13837.95</v>
+        <v>1195</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>72.26000000000001</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>86350.7</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="I7" s="7" t="n">
@@ -2277,7 +2290,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>tight_stop</t>
         </is>
       </c>
     </row>
@@ -2289,12 +2302,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>NUE</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="D8" s="17" t="inlineStr">
@@ -2303,17 +2316,17 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>329</v>
+        <v>670</v>
       </c>
       <c r="F8" s="13" t="n">
-        <v>250.49</v>
+        <v>213.56</v>
       </c>
       <c r="G8" s="13" t="n">
-        <v>82411.21000000001</v>
+        <v>143087.88</v>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>materials</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I8" s="17" t="n">
@@ -2321,7 +2334,7 @@
       </c>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t>conservative</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
     </row>
@@ -2333,12 +2346,12 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>INTU</t>
+          <t>REGN</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -2347,17 +2360,17 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-82</v>
+        <v>-23</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>284.22</v>
+        <v>601.65</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>-23306.04</v>
+        <v>-13837.95</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I9" s="7" t="n">
@@ -2365,7 +2378,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>conservative</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2390,7 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
@@ -2409,7 +2422,7 @@
       </c>
       <c r="J10" s="17" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>conservative</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2434,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>MKTX</t>
+          <t>INTU</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2435,13 +2448,13 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-422</v>
+        <v>-82</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>116.11</v>
+        <v>284.22</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>-48998.42</v>
+        <v>-23306.04</v>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
@@ -2453,7 +2466,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>conservative</t>
         </is>
       </c>
     </row>
@@ -2465,12 +2478,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>STLD</t>
+          <t>NUE</t>
         </is>
       </c>
       <c r="D12" s="17" t="inlineStr">
@@ -2479,13 +2492,13 @@
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>386</v>
+        <v>329</v>
       </c>
       <c r="F12" s="13" t="n">
-        <v>268.34</v>
+        <v>250.49</v>
       </c>
       <c r="G12" s="13" t="n">
-        <v>103579.24</v>
+        <v>82411.21000000001</v>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
@@ -2493,11 +2506,11 @@
         </is>
       </c>
       <c r="I12" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="17" t="inlineStr">
         <is>
-          <t>no_reversal_protection</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2522,12 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
+          <t>NUE/MKTX</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>MKTX</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2523,25 +2536,25 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-358</v>
+        <v>-422</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>144.82</v>
+        <v>116.11</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>-51845.56</v>
+        <v>-48998.42</v>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>no_reversal_protection</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2566,7 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>STLD/FMC</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
@@ -2567,13 +2580,13 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>628</v>
+        <v>386</v>
       </c>
       <c r="F14" s="13" t="n">
         <v>268.34</v>
       </c>
       <c r="G14" s="13" t="n">
-        <v>168517.52</v>
+        <v>103579.24</v>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
@@ -2585,7 +2598,7 @@
       </c>
       <c r="J14" s="17" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>no_reversal_protection</t>
         </is>
       </c>
     </row>
@@ -2597,12 +2610,12 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>STLD/FMC</t>
+          <t>STLD/UHS</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>FMC</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2611,17 +2624,17 @@
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-6843</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>10.8</v>
+        <v>-358</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>144.82</v>
       </c>
       <c r="G15" s="19" t="n">
-        <v>-73904.39999999999</v>
+        <v>-51845.56</v>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>health</t>
         </is>
       </c>
       <c r="I15" s="7" t="n">
@@ -2629,7 +2642,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>no_reversal_protection</t>
         </is>
       </c>
     </row>
@@ -2641,12 +2654,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>STLD</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -2655,25 +2668,25 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>2247</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>23.95</v>
+        <v>628</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>268.34</v>
       </c>
       <c r="G16" s="13" t="n">
-        <v>53815.65</v>
+        <v>168517.52</v>
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>realestate</t>
+          <t>materials</t>
         </is>
       </c>
       <c r="I16" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="17" t="inlineStr">
         <is>
-          <t>long_term_kalman</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2685,12 +2698,12 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>MOS</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2699,13 +2712,13 @@
         </is>
       </c>
       <c r="E17" s="24" t="n">
-        <v>-2168</v>
+        <v>-6843</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>19.82</v>
+        <v>10.8</v>
       </c>
       <c r="G17" s="19" t="n">
-        <v>-42969.76</v>
+        <v>-73904.39999999999</v>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
@@ -2713,11 +2726,11 @@
         </is>
       </c>
       <c r="I17" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>long_term_kalman</t>
+          <t>aggressive</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2742,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="D18" s="17" t="inlineStr">
@@ -2743,17 +2756,17 @@
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>470</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>213.56</v>
+        <v>2247</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <v>23.95</v>
       </c>
       <c r="G18" s="13" t="n">
-        <v>100375.08</v>
+        <v>53815.65</v>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>realestate</t>
         </is>
       </c>
       <c r="I18" s="17" t="n">
@@ -2761,7 +2774,7 @@
       </c>
       <c r="J18" s="17" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>long_term_kalman</t>
         </is>
       </c>
     </row>
@@ -2773,12 +2786,12 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>TRMB</t>
+          <t>MOS</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -2787,17 +2800,17 @@
         </is>
       </c>
       <c r="E19" s="24" t="n">
-        <v>-972</v>
+        <v>-2168</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>50.6</v>
+        <v>19.82</v>
       </c>
       <c r="G19" s="19" t="n">
-        <v>-49183.2</v>
+        <v>-42969.76</v>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>industrial</t>
+          <t>food</t>
         </is>
       </c>
       <c r="I19" s="7" t="n">
@@ -2805,7 +2818,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>long_term_kalman</t>
         </is>
       </c>
     </row>
@@ -2817,12 +2830,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>UNH/ULTA</t>
+          <t>KLAC/TRMB</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="D20" s="17" t="inlineStr">
@@ -2831,17 +2844,17 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>124</v>
+        <v>470</v>
       </c>
       <c r="F20" s="13" t="n">
-        <v>407.46</v>
+        <v>213.56</v>
       </c>
       <c r="G20" s="13" t="n">
-        <v>50525.04</v>
+        <v>100375.08</v>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="I20" s="17" t="n">
@@ -2849,7 +2862,7 @@
       </c>
       <c r="J20" s="17" t="inlineStr">
         <is>
-          <t>short_term_beta_neutral</t>
+          <t>monthly_aligned_windows</t>
         </is>
       </c>
     </row>
@@ -2861,37 +2874,125 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
+          <t>KLAC/TRMB</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="n">
+        <v>-972</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="G21" s="19" t="n">
+        <v>-49183.2</v>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>industrial</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>monthly_aligned_windows</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>MTFS</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
           <t>UNH/ULTA</t>
         </is>
       </c>
-      <c r="C21" s="7" t="inlineStr">
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>UNH</t>
+        </is>
+      </c>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>124</v>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>407.46</v>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>50525.04</v>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="17" t="inlineStr">
+        <is>
+          <t>short_term_beta_neutral</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>MTFS</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>UNH/ULTA</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>ULTA</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="E21" s="24" t="n">
+      <c r="E23" s="24" t="n">
         <v>-107</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F23" s="4" t="n">
         <v>470.75</v>
       </c>
-      <c r="G21" s="19" t="n">
+      <c r="G23" s="19" t="n">
         <v>-50370.25</v>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>food</t>
         </is>
       </c>
-      <c r="I21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="I23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
         <is>
           <t>short_term_beta_neutral</t>
         </is>
@@ -2911,7 +3012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3001,31 +3102,31 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>MTFS</t>
+          <t>MRPT</t>
         </is>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>KLAC/REGN</t>
+          <t>BSX/WMB</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9083.059999999999</v>
+        <v>1927.19</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>156925.83</v>
+        <v>174184.48</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>beta_neutral_long_term</t>
+          <t>tight_stop</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
     </row>
@@ -3037,21 +3138,21 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>NUE/INTU</t>
+          <t>KLAC/REGN</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>4040.63</v>
+        <v>9083.059999999999</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>105717.25</v>
+        <v>156925.83</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>conservative</t>
+          <t>beta_neutral_long_term</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -3068,21 +3169,21 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>NUE/MKTX</t>
+          <t>NUE/INTU</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6039.67</v>
+        <v>4040.63</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>131409.63</v>
+        <v>105717.25</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>weekly_aligned_windows</t>
+          <t>conservative</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -3099,21 +3200,21 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>STLD/UHS</t>
-        </is>
-      </c>
-      <c r="C8" s="35" t="n">
-        <v>-8.06</v>
+          <t>NUE/MKTX</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>6039.67</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>155424.8</v>
+        <v>131409.63</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t>no_reversal_protection</t>
+          <t>weekly_aligned_windows</t>
         </is>
       </c>
       <c r="G8" s="17" t="inlineStr">
@@ -3130,21 +3231,21 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>STLD/FMC</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>2768.82</v>
+          <t>STLD/UHS</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="n">
+        <v>-8.06</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>242421.92</v>
+        <v>155424.8</v>
       </c>
       <c r="E9" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>no_reversal_protection</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
@@ -3161,21 +3262,21 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>STLD/FMC</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>2281.05</v>
+        <v>2768.82</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>96785.41</v>
+        <v>242421.92</v>
       </c>
       <c r="E10" s="17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t>long_term_kalman</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="G10" s="17" t="inlineStr">
@@ -3192,21 +3293,21 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>KLAC/TRMB</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>2108.89</v>
+        <v>2281.05</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>149558.28</v>
+        <v>96785.41</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>monthly_aligned_windows</t>
+          <t>long_term_kalman</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -3223,24 +3324,55 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
+          <t>KLAC/TRMB</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>2108.89</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>149558.28</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>monthly_aligned_windows</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>MTFS</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
           <t>UNH/ULTA</t>
         </is>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C13" s="11" t="n">
         <v>78.09</v>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D13" s="4" t="n">
         <v>100895.29</v>
       </c>
-      <c r="E12" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E13" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>short_term_beta_neutral</t>
         </is>
       </c>
-      <c r="G12" s="17" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>long</t>
         </is>
@@ -3374,7 +3506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3534,7 +3666,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>26.79</v>
+        <v>24.4</v>
       </c>
     </row>
     <row r="14">
@@ -3544,7 +3676,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>23.44</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="15">
@@ -3554,7 +3686,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>16.37</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="16">
@@ -3564,7 +3696,7 @@
         </is>
       </c>
       <c r="B16" s="17" t="n">
-        <v>10.98</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="17">
@@ -3574,7 +3706,7 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>8.15</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="18">
@@ -3584,27 +3716,27 @@
         </is>
       </c>
       <c r="B18" s="17" t="n">
-        <v>7.88</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>HST/MOS</t>
+          <t>BSX/WMB</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>3.65</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>HAS/PFE</t>
+          <t>HST/MOS</t>
         </is>
       </c>
       <c r="B20" s="17" t="n">
-        <v>1.44</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="21">
@@ -3614,7 +3746,17 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>HAS/PFE</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>
@@ -4110,7 +4252,7 @@
         <v>1.97</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>1.243</v>
+        <v>1.409</v>
       </c>
     </row>
     <row r="10">
@@ -4144,7 +4286,7 @@
         <v>2.64</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>0.304</v>
+        <v>0.612</v>
       </c>
     </row>
     <row r="11">
@@ -4253,7 +4395,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>175909.04</v>
+        <v>87801.67</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>136845.07</v>
@@ -4272,7 +4414,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>450206.36</v>
+        <v>539796.8100000001</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>500708.01</v>
@@ -4291,7 +4433,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>869810.6899999999</v>
+        <v>956161.39</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>909026.52</v>
@@ -4310,7 +4452,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>1495926.09</v>
+        <v>1583759.87</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>1546579.6</v>
@@ -4329,7 +4471,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>441378.78</v>
+        <v>529212.5600000001</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>490890.21</v>
@@ -4367,7 +4509,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>441378.78</v>
+        <v>529212.5600000001</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>490890.21</v>
@@ -4405,7 +4547,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>1.243</v>
+        <v>1.409</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>1.326</v>
@@ -4424,7 +4566,7 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>0.406</v>
+        <v>0.405</v>
       </c>
       <c r="C14" s="17" t="n">
         <v>0.396</v>
@@ -4443,7 +4585,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>262237.89</v>
+        <v>297074.79</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>279983.35</v>
@@ -4462,7 +4604,7 @@
         </is>
       </c>
       <c r="B16" s="13" t="n">
-        <v>792309.42</v>
+        <v>757472.52</v>
       </c>
       <c r="C16" s="13" t="n">
         <v>775706.04</v>
@@ -4534,7 +4676,7 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>869810.6899999999</v>
+        <v>956161.39</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>909026.52</v>
@@ -4572,7 +4714,7 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>869810.6899999999</v>
+        <v>956161.39</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>909026.52</v>
@@ -4610,7 +4752,7 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>869810.6899999999</v>
+        <v>956161.39</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>909026.52</v>
@@ -4629,7 +4771,7 @@
         </is>
       </c>
       <c r="B26" s="13" t="n">
-        <v>8827.58</v>
+        <v>10584.25</v>
       </c>
       <c r="C26" s="13" t="n">
         <v>9817.799999999999</v>
@@ -4648,7 +4790,7 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>8827.58</v>
+        <v>10584.25</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>9817.799999999999</v>
@@ -4667,7 +4809,7 @@
         </is>
       </c>
       <c r="B28" s="13" t="n">
-        <v>441378.78</v>
+        <v>529212.5600000001</v>
       </c>
       <c r="C28" s="13" t="n">
         <v>490890.21</v>
@@ -4686,7 +4828,7 @@
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>441378.78</v>
+        <v>529212.5600000001</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>490890.21</v>
@@ -4724,7 +4866,7 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>8827.58</v>
+        <v>10584.25</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>9817.799999999999</v>
@@ -4743,7 +4885,7 @@
         </is>
       </c>
       <c r="B32" s="13" t="n">
-        <v>175909.04</v>
+        <v>87801.67</v>
       </c>
       <c r="C32" s="13" t="n">
         <v>136845.07</v>
@@ -4834,7 +4976,7 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>478787.36</v>
+        <v>390679.98</v>
       </c>
       <c r="C39" s="4" t="n">
         <v>468937.27</v>
@@ -4853,7 +4995,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>88702.46000000001</v>
+        <v>178292.92</v>
       </c>
       <c r="C40" s="13" t="n">
         <v>99198.59</v>
@@ -4872,7 +5014,7 @@
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>85087.86</v>
+        <v>171438.56</v>
       </c>
       <c r="C41" s="4" t="n">
         <v>96238.08</v>
@@ -4891,7 +5033,7 @@
         </is>
       </c>
       <c r="B42" s="13" t="n">
-        <v>652577.6800000001</v>
+        <v>740411.46</v>
       </c>
       <c r="C42" s="13" t="n">
         <v>664373.9399999999</v>
@@ -4910,7 +5052,7 @@
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>86963.2</v>
+        <v>174796.98</v>
       </c>
       <c r="C43" s="4" t="n">
         <v>97253.52</v>
@@ -4948,7 +5090,7 @@
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>86963.2</v>
+        <v>174796.98</v>
       </c>
       <c r="C45" s="4" t="n">
         <v>97253.52</v>
@@ -4986,7 +5128,7 @@
         </is>
       </c>
       <c r="B47" s="7" t="n">
-        <v>0.304</v>
+        <v>0.612</v>
       </c>
       <c r="C47" s="7" t="n">
         <v>0.341</v>
@@ -5005,7 +5147,7 @@
         </is>
       </c>
       <c r="B48" s="17" t="n">
-        <v>-0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="C48" s="17" t="n">
         <v>-0.002</v>
@@ -5024,7 +5166,7 @@
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>34410.21</v>
+        <v>69247.11</v>
       </c>
       <c r="C49" s="4" t="n">
         <v>38698.32</v>
@@ -5043,7 +5185,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>531204.27</v>
+        <v>496367.37</v>
       </c>
       <c r="C50" s="13" t="n">
         <v>528422.1</v>
@@ -5115,7 +5257,7 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>85087.86</v>
+        <v>171438.56</v>
       </c>
       <c r="C55" s="4" t="n">
         <v>96238.08</v>
@@ -5153,7 +5295,7 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>85087.86</v>
+        <v>171438.56</v>
       </c>
       <c r="C57" s="4" t="n">
         <v>96238.08</v>
@@ -5191,7 +5333,7 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>85087.86</v>
+        <v>171438.56</v>
       </c>
       <c r="C59" s="4" t="n">
         <v>96238.08</v>
@@ -5210,7 +5352,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>1739.26</v>
+        <v>3495.94</v>
       </c>
       <c r="C60" s="13" t="n">
         <v>1945.07</v>
@@ -5229,7 +5371,7 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>1739.26</v>
+        <v>3495.94</v>
       </c>
       <c r="C61" s="4" t="n">
         <v>1945.07</v>
@@ -5248,7 +5390,7 @@
         </is>
       </c>
       <c r="B62" s="13" t="n">
-        <v>86963.2</v>
+        <v>174796.98</v>
       </c>
       <c r="C62" s="13" t="n">
         <v>97253.52</v>
@@ -5267,7 +5409,7 @@
         </is>
       </c>
       <c r="B63" s="4" t="n">
-        <v>86963.2</v>
+        <v>174796.98</v>
       </c>
       <c r="C63" s="4" t="n">
         <v>97253.52</v>
@@ -5305,7 +5447,7 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
-        <v>1739.26</v>
+        <v>3495.94</v>
       </c>
       <c r="C65" s="4" t="n">
         <v>1945.07</v>
@@ -5324,7 +5466,7 @@
         </is>
       </c>
       <c r="B66" s="13" t="n">
-        <v>478787.36</v>
+        <v>390679.98</v>
       </c>
       <c r="C66" s="13" t="n">
         <v>468937.27</v>
@@ -6065,7 +6207,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>24694.87</v>
+        <v>26622.06</v>
       </c>
     </row>
     <row r="9">
@@ -6146,8 +6288,8 @@
           <t>Current unrealized PnL</t>
         </is>
       </c>
-      <c r="B13" s="19" t="n">
-        <v>-1697.28</v>
+      <c r="B13" s="4" t="n">
+        <v>229.91</v>
       </c>
     </row>
     <row r="15">
@@ -6828,7 +6970,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>616536.01</v>
+        <v>618019.09</v>
       </c>
     </row>
     <row r="6">
@@ -6848,7 +6990,7 @@
         </is>
       </c>
       <c r="B7" s="19" t="n">
-        <v>-373379.97</v>
+        <v>-371896.89</v>
       </c>
     </row>
     <row r="8">
@@ -6868,7 +7010,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>175909.04</v>
+        <v>87801.67</v>
       </c>
     </row>
     <row r="11">
@@ -8543,31 +8685,31 @@
         <v>1054547.31</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>869810.6899999999</v>
+        <v>956161.39</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>441378.78</v>
+        <v>529212.5600000001</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1311189.47</v>
+        <v>1485373.95</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>428431.91</v>
+        <v>426948.83</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>1.243</v>
+        <v>1.409</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.406</v>
+        <v>0.405</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>124.34</v>
+        <v>140.85</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>62.17</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="K4" s="24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -8580,31 +8722,31 @@
         <v>565614.48</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>85087.86</v>
+        <v>171438.56</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>86963.2</v>
+        <v>174796.98</v>
       </c>
       <c r="E5" s="13" t="n">
-        <v>172051.06</v>
+        <v>346235.54</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>-1875.34</v>
+        <v>-3358.42</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>0.304</v>
+        <v>0.612</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>-0.003</v>
+        <v>-0.006</v>
       </c>
       <c r="I5" s="25" t="n">
-        <v>30.42</v>
+        <v>61.21</v>
       </c>
       <c r="J5" s="25" t="n">
-        <v>15.21</v>
+        <v>30.61</v>
       </c>
       <c r="K5" s="26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -8658,7 +8800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8679,7 +8821,7 @@
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
-          <t>HHI=0.1207  ·  effective N pairs=8.3  ·  max pair=18.49% of gross</t>
+          <t>HHI=0.1078  ·  effective N pairs=9.3  ·  max pair=16.32% of gross</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8873,7 @@
         <v>25.8</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>20.75</v>
+        <v>18.32</v>
       </c>
       <c r="F6" s="24" t="n">
         <v>2</v>
@@ -8753,7 +8895,7 @@
         <v>23.09</v>
       </c>
       <c r="E7" s="21" t="n">
-        <v>18.57</v>
+        <v>16.39</v>
       </c>
       <c r="F7" s="26" t="n">
         <v>2</v>
@@ -8775,7 +8917,7 @@
         <v>15.63</v>
       </c>
       <c r="E8" s="23" t="n">
-        <v>12.57</v>
+        <v>11.1</v>
       </c>
       <c r="F8" s="24" t="n">
         <v>2</v>
@@ -8784,20 +8926,20 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>BSX</t>
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>86963.2</v>
+        <v>87833.78</v>
       </c>
       <c r="C9" s="18" t="n">
-        <v>-86963.2</v>
+        <v>-87833.78</v>
       </c>
       <c r="D9" s="21" t="n">
-        <v>8.25</v>
+        <v>8.33</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>6.63</v>
+        <v>5.91</v>
       </c>
       <c r="F9" s="26" t="n">
         <v>1</v>
@@ -8806,20 +8948,20 @@
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t>HAS</t>
+          <t>PFE</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>85087.86</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>85087.86</v>
+        <v>86963.2</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>-86963.2</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>8.07</v>
+        <v>8.25</v>
       </c>
       <c r="E10" s="23" t="n">
-        <v>6.49</v>
+        <v>5.85</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>1</v>
@@ -8828,20 +8970,20 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>FMC</t>
+          <t>WMB</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>73904.39999999999</v>
-      </c>
-      <c r="C11" s="18" t="n">
-        <v>-73904.39999999999</v>
+        <v>86350.7</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>86350.7</v>
       </c>
       <c r="D11" s="21" t="n">
-        <v>7.01</v>
+        <v>8.19</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>5.64</v>
+        <v>5.81</v>
       </c>
       <c r="F11" s="26" t="n">
         <v>1</v>
@@ -8850,20 +8992,20 @@
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>HST</t>
+          <t>HAS</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>53815.65</v>
+        <v>85087.86</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>53815.65</v>
+        <v>85087.86</v>
       </c>
       <c r="D12" s="23" t="n">
-        <v>5.1</v>
+        <v>8.07</v>
       </c>
       <c r="E12" s="23" t="n">
-        <v>4.1</v>
+        <v>5.73</v>
       </c>
       <c r="F12" s="24" t="n">
         <v>1</v>
@@ -8872,20 +9014,20 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>UHS</t>
+          <t>FMC</t>
         </is>
       </c>
       <c r="B13" s="13" t="n">
-        <v>51845.56</v>
+        <v>73904.39999999999</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>-51845.56</v>
+        <v>-73904.39999999999</v>
       </c>
       <c r="D13" s="21" t="n">
-        <v>4.92</v>
+        <v>7.01</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>3.95</v>
+        <v>4.98</v>
       </c>
       <c r="F13" s="26" t="n">
         <v>1</v>
@@ -8894,20 +9036,20 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>HST</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>50525.04</v>
+        <v>53815.65</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>50525.04</v>
+        <v>53815.65</v>
       </c>
       <c r="D14" s="23" t="n">
-        <v>4.79</v>
+        <v>5.1</v>
       </c>
       <c r="E14" s="23" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="F14" s="24" t="n">
         <v>1</v>
@@ -8916,20 +9058,20 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>ULTA</t>
+          <t>UHS</t>
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>50370.25</v>
+        <v>51845.56</v>
       </c>
       <c r="C15" s="18" t="n">
-        <v>-50370.25</v>
+        <v>-51845.56</v>
       </c>
       <c r="D15" s="21" t="n">
-        <v>4.78</v>
+        <v>4.92</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>3.84</v>
+        <v>3.49</v>
       </c>
       <c r="F15" s="26" t="n">
         <v>1</v>
@@ -8985,102 +9127,121 @@
         <v>436919.18</v>
       </c>
       <c r="E20" s="7" t="n">
-        <v>33.32</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>tech</t>
+          <t>health</t>
         </is>
       </c>
       <c r="B21" s="13" t="n">
-        <v>243462.96</v>
+        <v>50525.04</v>
       </c>
       <c r="C21" s="13" t="n">
-        <v>72304.46000000001</v>
-      </c>
-      <c r="D21" s="13" t="n">
-        <v>171158.5</v>
+        <v>240480.49</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <v>-189955.45</v>
       </c>
       <c r="E21" s="17" t="n">
-        <v>13.05</v>
+        <v>-12.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>tech</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>50525.04</v>
+        <v>243462.96</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>152646.71</v>
-      </c>
-      <c r="D22" s="19" t="n">
-        <v>-102121.67</v>
+        <v>72304.46000000001</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>171158.5</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>-7.79</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="B23" s="13" t="n">
-        <v>85087.86</v>
-      </c>
-      <c r="C23" s="13" t="n">
-        <v>167244.41</v>
-      </c>
-      <c r="D23" s="18" t="n">
-        <v>-82156.55</v>
+        <v>86350.7</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>86350.7</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>-6.27</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>realestate</t>
+          <t>food</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>53815.65</v>
-      </c>
-      <c r="C24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>53815.65</v>
+        <v>85087.86</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>167244.41</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>-82156.55</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>4.1</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
+          <t>realestate</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>53815.65</v>
+      </c>
+      <c r="C25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>53815.65</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="13" t="n">
+      <c r="B26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="n">
         <v>49183.2</v>
       </c>
-      <c r="D25" s="18" t="n">
+      <c r="D26" s="19" t="n">
         <v>-49183.2</v>
       </c>
-      <c r="E25" s="17" t="n">
-        <v>-3.75</v>
+      <c r="E26" s="7" t="n">
+        <v>-3.31</v>
       </c>
     </row>
   </sheetData>
@@ -9097,7 +9258,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9118,7 +9279,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>0.804</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="4">
@@ -9128,7 +9289,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>1.284</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="5">
@@ -9179,57 +9340,67 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>33.32</v>
+        <v>29.41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>tech</t>
-        </is>
-      </c>
-      <c r="B11" s="21" t="n">
-        <v>13.05</v>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="n">
+        <v>-12.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>health</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="n">
-        <v>-7.79</v>
+          <t>tech</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>11.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="n">
-        <v>-6.27</v>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>5.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>realestate</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="n">
-        <v>4.1</v>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="B14" s="22" t="n">
+        <v>-5.53</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
+          <t>realestate</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="n">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
           <t>industrial</t>
         </is>
       </c>
-      <c r="B15" s="20" t="n">
-        <v>-3.75</v>
+      <c r="B16" s="22" t="n">
+        <v>-3.31</v>
       </c>
     </row>
   </sheetData>
